--- a/public/template/template_upload_kontrak.xlsx
+++ b/public/template/template_upload_kontrak.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ba44de7df4c40bc/Documents/HRIS - PT TRI CENTRUM FORTUNA/CODE/tcf-superapps/public/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\hris-prod\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{545BC130-A4FB-4FF5-BBFA-C70B407E8504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C235118C-18F2-4AE2-B135-FE62D02FCFDC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FC4D80-4D76-43E7-BD19-C642AF1ABE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9D850D6C-A414-4510-85CE-67383360A39D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D850D6C-A414-4510-85CE-67383360A39D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -106,6 +106,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -179,11 +182,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,22 +503,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D0E4EC-B375-444C-A099-75B908B6C530}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.54296875" customWidth="1"/>
+    <col min="1" max="1" width="41.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.5546875" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="36.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.7265625" customWidth="1"/>
-    <col min="9" max="9" width="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.77734375" customWidth="1"/>
+    <col min="9" max="9" width="33" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.21875" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -549,7 +553,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -574,18 +578,18 @@
       <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="K2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I16" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I16" s="4" t="s">
         <v>6</v>
       </c>
     </row>
